--- a/FinalReport/SomeGraphs.xlsx
+++ b/FinalReport/SomeGraphs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wendelin_ou/Documents/UWM_ECE757/CS757_FinalProject/FinalReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A87D47C-9670-BC4D-90EA-F45569B846BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8BA507-3D62-8446-970E-A6495FA0F874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="1360" windowWidth="27700" windowHeight="16680" activeTab="6" xr2:uid="{F8E42BA8-713A-FD49-BFDD-5ED621C02FB7}"/>
+    <workbookView xWindow="1460" yWindow="1360" windowWidth="27700" windowHeight="16680" activeTab="2" xr2:uid="{F8E42BA8-713A-FD49-BFDD-5ED621C02FB7}"/>
   </bookViews>
   <sheets>
     <sheet name="c1335" sheetId="4" r:id="rId1"/>
